--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123552033</v>
+        <v>123550280</v>
       </c>
       <c r="B4" t="n">
-        <v>95150</v>
+        <v>91003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,42 +937,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580554</v>
+        <v>580691</v>
       </c>
       <c r="R4" t="n">
-        <v>6485132</v>
+        <v>6485068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1018,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,17 +1029,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123550180</v>
+        <v>123551722</v>
       </c>
       <c r="B5" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,14 +1076,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 510 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580575</v>
+        <v>580736</v>
       </c>
       <c r="R5" t="n">
-        <v>6485039</v>
+        <v>6485061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123551970</v>
+        <v>123552033</v>
       </c>
       <c r="B6" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,14 +1188,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580608</v>
+        <v>580554</v>
       </c>
       <c r="R6" t="n">
-        <v>6485084</v>
+        <v>6485132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,11 +1243,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1266,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123552127</v>
+        <v>123550180</v>
       </c>
       <c r="B7" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,14 +1300,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 510 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580535</v>
+        <v>580575</v>
       </c>
       <c r="R7" t="n">
-        <v>6485004</v>
+        <v>6485039</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1354,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1378,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123551722</v>
+        <v>123552127</v>
       </c>
       <c r="B8" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,14 +1412,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580736</v>
+        <v>580535</v>
       </c>
       <c r="R8" t="n">
-        <v>6485061</v>
+        <v>6485004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1466,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1490,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123550280</v>
+        <v>123551970</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>95167</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,41 +1496,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580691</v>
+        <v>580608</v>
       </c>
       <c r="R9" t="n">
-        <v>6485068</v>
+        <v>6485084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1578,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
         <v>123551698</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>123551916</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123550280</v>
+        <v>123551722</v>
       </c>
       <c r="B4" t="n">
-        <v>91003</v>
+        <v>95167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,41 +937,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580691</v>
+        <v>580736</v>
       </c>
       <c r="R4" t="n">
-        <v>6485068</v>
+        <v>6485061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,14 +1030,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123551722</v>
+        <v>123552033</v>
       </c>
       <c r="B5" t="n">
         <v>95167</v>
@@ -1076,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580736</v>
+        <v>580554</v>
       </c>
       <c r="R5" t="n">
-        <v>6485061</v>
+        <v>6485132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1131,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552033</v>
+        <v>123550280</v>
       </c>
       <c r="B6" t="n">
-        <v>95167</v>
+        <v>91003</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,42 +1161,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580554</v>
+        <v>580691</v>
       </c>
       <c r="R6" t="n">
-        <v>6485132</v>
+        <v>6485068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123551722</v>
+        <v>123551970</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,14 +965,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580736</v>
+        <v>580608</v>
       </c>
       <c r="R4" t="n">
-        <v>6485061</v>
+        <v>6485084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123552033</v>
+        <v>123551916</v>
       </c>
       <c r="B5" t="n">
-        <v>95167</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,42 +1054,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580554</v>
+        <v>580608</v>
       </c>
       <c r="R5" t="n">
-        <v>6485132</v>
+        <v>6485084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,6 +1149,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,7 +1174,7 @@
         <v>123550280</v>
       </c>
       <c r="B6" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,7 +1285,7 @@
         <v>123550180</v>
       </c>
       <c r="B7" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123552127</v>
+        <v>123552033</v>
       </c>
       <c r="B8" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,14 +1434,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580535</v>
+        <v>580554</v>
       </c>
       <c r="R8" t="n">
-        <v>6485004</v>
+        <v>6485132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123551970</v>
+        <v>123552127</v>
       </c>
       <c r="B9" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,14 +1546,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580608</v>
+        <v>580535</v>
       </c>
       <c r="R9" t="n">
-        <v>6485084</v>
+        <v>6485004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,11 +1601,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1601,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123551698</v>
+        <v>123551722</v>
       </c>
       <c r="B10" t="n">
-        <v>91003</v>
+        <v>95173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,30 +1630,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123551916</v>
+        <v>123551698</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,54 +1742,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580608</v>
+        <v>580736</v>
       </c>
       <c r="R11" t="n">
-        <v>6485084</v>
+        <v>6485061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,12 +1823,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123551970</v>
+        <v>123550180</v>
       </c>
       <c r="B4" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,14 +965,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 510 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580608</v>
+        <v>580575</v>
       </c>
       <c r="R4" t="n">
-        <v>6485084</v>
+        <v>6485039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,12 +1019,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123551916</v>
+        <v>123550280</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,54 +1049,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580608</v>
+        <v>580691</v>
       </c>
       <c r="R5" t="n">
-        <v>6485084</v>
+        <v>6485068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,12 +1130,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1171,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123550280</v>
+        <v>123552127</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,41 +1160,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580691</v>
+        <v>580535</v>
       </c>
       <c r="R6" t="n">
-        <v>6485068</v>
+        <v>6485004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1264,7 +1242,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,17 +1253,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123550180</v>
+        <v>123551916</v>
       </c>
       <c r="B7" t="n">
-        <v>95173</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,42 +1272,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 510 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580575</v>
+        <v>580608</v>
       </c>
       <c r="R7" t="n">
-        <v>6485039</v>
+        <v>6485084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,7 +1366,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123552033</v>
+        <v>123551970</v>
       </c>
       <c r="B8" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,14 +1429,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580554</v>
+        <v>580608</v>
       </c>
       <c r="R8" t="n">
-        <v>6485132</v>
+        <v>6485084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,6 +1484,11 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123552127</v>
+        <v>123551698</v>
       </c>
       <c r="B9" t="n">
-        <v>95173</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,42 +1518,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580535</v>
+        <v>580736</v>
       </c>
       <c r="R9" t="n">
-        <v>6485004</v>
+        <v>6485061</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1599,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1618,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123551722</v>
+        <v>123552033</v>
       </c>
       <c r="B10" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,14 +1657,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580736</v>
+        <v>580554</v>
       </c>
       <c r="R10" t="n">
-        <v>6485061</v>
+        <v>6485132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1711,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1730,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123551698</v>
+        <v>123551722</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>95175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,30 +1741,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123550180</v>
+        <v>123551722</v>
       </c>
       <c r="B4" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,14 +965,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 510 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580575</v>
+        <v>580736</v>
       </c>
       <c r="R4" t="n">
-        <v>6485039</v>
+        <v>6485061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123550280</v>
+        <v>123551970</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,41 +1049,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580691</v>
+        <v>580608</v>
       </c>
       <c r="R5" t="n">
-        <v>6485068</v>
+        <v>6485084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1131,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552127</v>
+        <v>123552033</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,14 +1194,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580535</v>
+        <v>580554</v>
       </c>
       <c r="R6" t="n">
-        <v>6485004</v>
+        <v>6485132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123551916</v>
+        <v>123550280</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,54 +1278,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580608</v>
+        <v>580691</v>
       </c>
       <c r="R7" t="n">
-        <v>6485084</v>
+        <v>6485068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,12 +1359,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123551970</v>
+        <v>123551916</v>
       </c>
       <c r="B8" t="n">
-        <v>95175</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1389,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123551698</v>
+        <v>123550180</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,41 +1518,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 510 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580736</v>
+        <v>580575</v>
       </c>
       <c r="R9" t="n">
-        <v>6485061</v>
+        <v>6485039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123552033</v>
+        <v>123551698</v>
       </c>
       <c r="B10" t="n">
-        <v>95175</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,42 +1630,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580554</v>
+        <v>580736</v>
       </c>
       <c r="R10" t="n">
-        <v>6485132</v>
+        <v>6485061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123551722</v>
+        <v>123552127</v>
       </c>
       <c r="B11" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,14 +1769,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580736</v>
+        <v>580535</v>
       </c>
       <c r="R11" t="n">
-        <v>6485061</v>
+        <v>6485004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123551722</v>
+        <v>123550180</v>
       </c>
       <c r="B4" t="n">
         <v>95683</v>
@@ -965,14 +965,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 510 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580736</v>
+        <v>580575</v>
       </c>
       <c r="R4" t="n">
-        <v>6485061</v>
+        <v>6485039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123551970</v>
+        <v>123552033</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1077,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580608</v>
+        <v>580554</v>
       </c>
       <c r="R5" t="n">
-        <v>6485084</v>
+        <v>6485132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,11 +1132,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552033</v>
+        <v>123551722</v>
       </c>
       <c r="B6" t="n">
         <v>95683</v>
@@ -1194,14 +1189,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580554</v>
+        <v>580736</v>
       </c>
       <c r="R6" t="n">
-        <v>6485132</v>
+        <v>6485061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123551916</v>
+        <v>123551970</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,42 +1384,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1506,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123550180</v>
+        <v>123551916</v>
       </c>
       <c r="B9" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,42 +1501,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 510 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580575</v>
+        <v>580608</v>
       </c>
       <c r="R9" t="n">
-        <v>6485039</v>
+        <v>6485084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1595,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123552033</v>
+        <v>123552127</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1077,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580554</v>
+        <v>580535</v>
       </c>
       <c r="R5" t="n">
-        <v>6485132</v>
+        <v>6485004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123551722</v>
+        <v>123552033</v>
       </c>
       <c r="B6" t="n">
         <v>95683</v>
@@ -1189,14 +1189,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580736</v>
+        <v>580554</v>
       </c>
       <c r="R6" t="n">
-        <v>6485061</v>
+        <v>6485132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123550280</v>
+        <v>123551916</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,41 +1273,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580691</v>
+        <v>580608</v>
       </c>
       <c r="R7" t="n">
-        <v>6485068</v>
+        <v>6485084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1367,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1372,7 +1390,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123551970</v>
+        <v>123551722</v>
       </c>
       <c r="B8" t="n">
         <v>95683</v>
@@ -1412,14 +1430,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580608</v>
+        <v>580736</v>
       </c>
       <c r="R8" t="n">
-        <v>6485084</v>
+        <v>6485061</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,12 +1484,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1489,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123551916</v>
+        <v>123550280</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,54 +1514,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580608</v>
+        <v>580691</v>
       </c>
       <c r="R9" t="n">
-        <v>6485084</v>
+        <v>6485068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,12 +1595,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1611,17 +1606,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123551698</v>
+        <v>123551970</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,41 +1625,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580736</v>
+        <v>580608</v>
       </c>
       <c r="R10" t="n">
-        <v>6485061</v>
+        <v>6485084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1707,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1729,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123552127</v>
+        <v>123551698</v>
       </c>
       <c r="B11" t="n">
-        <v>95683</v>
+        <v>91010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1742,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580535</v>
+        <v>580736</v>
       </c>
       <c r="R11" t="n">
-        <v>6485004</v>
+        <v>6485061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123550180</v>
+        <v>123551970</v>
       </c>
       <c r="B4" t="n">
         <v>95683</v>
@@ -965,14 +965,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 510 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580575</v>
+        <v>580608</v>
       </c>
       <c r="R4" t="n">
-        <v>6485039</v>
+        <v>6485084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,7 +1042,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123552127</v>
+        <v>123552033</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1077,14 +1082,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 555 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580535</v>
+        <v>580554</v>
       </c>
       <c r="R5" t="n">
-        <v>6485004</v>
+        <v>6485132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552033</v>
+        <v>123550280</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,42 +1166,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 555 m, Ög</t>
+          <t>Skällingtorp VNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580554</v>
+        <v>580691</v>
       </c>
       <c r="R6" t="n">
-        <v>6485132</v>
+        <v>6485068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1261,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123551916</v>
+        <v>123551722</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,54 +1277,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV 360 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580608</v>
+        <v>580736</v>
       </c>
       <c r="R7" t="n">
-        <v>6485084</v>
+        <v>6485061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,12 +1359,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1390,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123551722</v>
+        <v>123551698</v>
       </c>
       <c r="B8" t="n">
-        <v>95683</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,31 +1389,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1502,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123550280</v>
+        <v>123550180</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,41 +1500,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 410 m, Ög</t>
+          <t>Skällingtorp VNV 510 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580691</v>
+        <v>580575</v>
       </c>
       <c r="R9" t="n">
-        <v>6485068</v>
+        <v>6485039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,14 +1593,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123551970</v>
+        <v>123552127</v>
       </c>
       <c r="B10" t="n">
         <v>95683</v>
@@ -1653,14 +1640,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580608</v>
+        <v>580535</v>
       </c>
       <c r="R10" t="n">
-        <v>6485084</v>
+        <v>6485004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,11 +1695,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1730,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123551698</v>
+        <v>123551916</v>
       </c>
       <c r="B11" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,41 +1724,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 360 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580736</v>
+        <v>580608</v>
       </c>
       <c r="R11" t="n">
-        <v>6485061</v>
+        <v>6485084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1818,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 12567-2025 artfynd.xlsx
+++ b/artfynd/A 12567-2025 artfynd.xlsx
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123552127</v>
+        <v>123551916</v>
       </c>
       <c r="B10" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,42 +1612,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV-V 550 m, Ög</t>
+          <t>Skällingtorp VNV 490 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580535</v>
+        <v>580608</v>
       </c>
       <c r="R10" t="n">
-        <v>6485004</v>
+        <v>6485084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,6 +1707,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1712,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123551916</v>
+        <v>123552127</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,54 +1741,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skällingtorp VNV 490 m, Ög</t>
+          <t>Skällingtorp VNV-V 550 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580608</v>
+        <v>580535</v>
       </c>
       <c r="R11" t="n">
-        <v>6485084</v>
+        <v>6485004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,11 +1824,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog med graninslag</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
